--- a/public/kk-gabji.xlsx
+++ b/public/kk-gabji.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10802"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{965C0FC5-6825-9647-954E-80FBFC888E66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09CB0C87-BC95-5E4E-BCC5-DB48C5026463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13660" yWindow="720" windowWidth="38400" windowHeight="19060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19200" yWindow="600" windowWidth="19200" windowHeight="19140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="양식" sheetId="1" r:id="rId1"/>
@@ -250,10 +250,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>{{부속}}</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>{{시공팀요청}}</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -266,10 +262,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">부속 </t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>날짜</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -294,6 +286,14 @@
   </si>
   <si>
     <t>발행처로고</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>부속비고</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{부속비고}}</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -617,7 +617,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -628,49 +628,16 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -678,17 +645,86 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -696,77 +732,26 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1115,947 +1100,887 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="24" customHeight="1">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="18" t="s">
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="18"/>
-      <c r="R1" s="18"/>
-      <c r="S1" s="18"/>
-      <c r="T1" s="19"/>
-      <c r="U1" s="19"/>
-      <c r="V1" s="19"/>
-      <c r="W1" s="19"/>
-      <c r="X1" s="19"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="47"/>
+      <c r="P1" s="47"/>
+      <c r="Q1" s="47"/>
+      <c r="R1" s="47"/>
+      <c r="S1" s="47"/>
+      <c r="T1" s="8"/>
+      <c r="U1" s="8"/>
+      <c r="V1" s="8"/>
+      <c r="W1" s="8"/>
+      <c r="X1" s="8"/>
       <c r="Z1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="24" customHeight="1">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
-      <c r="N2" s="18"/>
-      <c r="O2" s="18"/>
-      <c r="P2" s="18"/>
-      <c r="Q2" s="18"/>
-      <c r="R2" s="18"/>
-      <c r="S2" s="18"/>
-      <c r="T2" s="19"/>
-      <c r="U2" s="19"/>
-      <c r="V2" s="19"/>
-      <c r="W2" s="19"/>
-      <c r="X2" s="19"/>
-    </row>
-    <row r="3" spans="1:30" s="7" customFormat="1" ht="24" customHeight="1" thickBot="1">
-      <c r="A3" s="15" t="s">
+      <c r="A2" s="48"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="47"/>
+      <c r="S2" s="47"/>
+      <c r="T2" s="8"/>
+      <c r="U2" s="8"/>
+      <c r="V2" s="8"/>
+      <c r="W2" s="8"/>
+      <c r="X2" s="8"/>
+    </row>
+    <row r="3" spans="1:30" s="6" customFormat="1" ht="24" customHeight="1" thickBot="1">
+      <c r="A3" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="15"/>
-      <c r="O3" s="15"/>
-      <c r="P3" s="15"/>
-      <c r="Q3" s="15"/>
-      <c r="R3" s="15"/>
-      <c r="S3" s="15"/>
-      <c r="T3" s="15"/>
-      <c r="U3" s="15"/>
-      <c r="V3" s="15"/>
-      <c r="W3" s="15"/>
-      <c r="X3" s="15"/>
-    </row>
-    <row r="4" spans="1:30" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A4" s="9" t="s">
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="20"/>
+      <c r="Q3" s="20"/>
+      <c r="R3" s="20"/>
+      <c r="S3" s="20"/>
+      <c r="T3" s="20"/>
+      <c r="U3" s="20"/>
+      <c r="V3" s="20"/>
+      <c r="W3" s="20"/>
+      <c r="X3" s="20"/>
+    </row>
+    <row r="4" spans="1:30" s="6" customFormat="1" ht="24" customHeight="1">
+      <c r="A4" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="37" t="s">
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="37"/>
-      <c r="J4" s="37"/>
-      <c r="K4" s="37"/>
-      <c r="L4" s="37"/>
-      <c r="M4" s="37"/>
-      <c r="N4" s="37"/>
-      <c r="O4" s="37"/>
-      <c r="P4" s="37"/>
-      <c r="Q4" s="37"/>
-      <c r="R4" s="37"/>
-      <c r="S4" s="37"/>
-      <c r="T4" s="37"/>
-      <c r="U4" s="37"/>
-      <c r="V4" s="37"/>
-      <c r="W4" s="37"/>
-      <c r="X4" s="38"/>
-    </row>
-    <row r="5" spans="1:30" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A5" s="11" t="s">
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
+      <c r="N4" s="21"/>
+      <c r="O4" s="21"/>
+      <c r="P4" s="21"/>
+      <c r="Q4" s="21"/>
+      <c r="R4" s="21"/>
+      <c r="S4" s="21"/>
+      <c r="T4" s="21"/>
+      <c r="U4" s="21"/>
+      <c r="V4" s="21"/>
+      <c r="W4" s="21"/>
+      <c r="X4" s="22"/>
+    </row>
+    <row r="5" spans="1:30" s="6" customFormat="1" ht="24" customHeight="1">
+      <c r="A5" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="36" t="s">
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="36"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="36"/>
-      <c r="M5" s="12" t="s">
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12"/>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="36" t="s">
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="R5" s="36"/>
-      <c r="S5" s="36"/>
-      <c r="T5" s="36"/>
-      <c r="U5" s="36"/>
-      <c r="V5" s="36"/>
-      <c r="W5" s="36"/>
-      <c r="X5" s="40"/>
-      <c r="Z5" s="8"/>
-    </row>
-    <row r="6" spans="1:30" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A6" s="11" t="s">
+      <c r="R5" s="15"/>
+      <c r="S5" s="15"/>
+      <c r="T5" s="15"/>
+      <c r="U5" s="15"/>
+      <c r="V5" s="15"/>
+      <c r="W5" s="15"/>
+      <c r="X5" s="16"/>
+    </row>
+    <row r="6" spans="1:30" s="6" customFormat="1" ht="24" customHeight="1">
+      <c r="A6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="36" t="s">
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="36"/>
-      <c r="K6" s="36"/>
-      <c r="L6" s="36"/>
-      <c r="M6" s="12" t="s">
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="N6" s="12"/>
-      <c r="O6" s="12"/>
-      <c r="P6" s="12"/>
-      <c r="Q6" s="36" t="s">
+      <c r="N6" s="23"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="23"/>
+      <c r="Q6" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="R6" s="36"/>
-      <c r="S6" s="36"/>
-      <c r="T6" s="36"/>
-      <c r="U6" s="36"/>
-      <c r="V6" s="36"/>
-      <c r="W6" s="36"/>
-      <c r="X6" s="40"/>
-    </row>
-    <row r="7" spans="1:30" s="7" customFormat="1" ht="24" customHeight="1" thickBot="1">
-      <c r="A7" s="13" t="s">
+      <c r="R6" s="15"/>
+      <c r="S6" s="15"/>
+      <c r="T6" s="15"/>
+      <c r="U6" s="15"/>
+      <c r="V6" s="15"/>
+      <c r="W6" s="15"/>
+      <c r="X6" s="16"/>
+    </row>
+    <row r="7" spans="1:30" s="6" customFormat="1" ht="24" customHeight="1" thickBot="1">
+      <c r="A7" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="39" t="s">
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="F7" s="39"/>
-      <c r="G7" s="39"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="39"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="39"/>
-      <c r="M7" s="14" t="s">
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="18"/>
+      <c r="M7" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="N7" s="14"/>
-      <c r="O7" s="14"/>
-      <c r="P7" s="14"/>
-      <c r="Q7" s="39" t="s">
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="17"/>
+      <c r="Q7" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="R7" s="18"/>
+      <c r="S7" s="18"/>
+      <c r="T7" s="18"/>
+      <c r="U7" s="18"/>
+      <c r="V7" s="18"/>
+      <c r="W7" s="18"/>
+      <c r="X7" s="19"/>
+    </row>
+    <row r="8" spans="1:30" s="6" customFormat="1" ht="24" customHeight="1">
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="7"/>
+      <c r="X8" s="7"/>
+    </row>
+    <row r="9" spans="1:30" s="6" customFormat="1" ht="24" customHeight="1" thickBot="1">
+      <c r="A9" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="20"/>
+      <c r="T9" s="20"/>
+      <c r="U9" s="20"/>
+      <c r="V9" s="20"/>
+      <c r="W9" s="20"/>
+      <c r="X9" s="20"/>
+    </row>
+    <row r="10" spans="1:30" s="6" customFormat="1" ht="24" customHeight="1">
+      <c r="A10" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="24"/>
+      <c r="L10" s="24"/>
+      <c r="M10" s="24"/>
+      <c r="N10" s="24"/>
+      <c r="O10" s="24"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="24"/>
+      <c r="R10" s="24"/>
+      <c r="S10" s="24"/>
+      <c r="T10" s="24"/>
+      <c r="U10" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="V10" s="24"/>
+      <c r="W10" s="24"/>
+      <c r="X10" s="25"/>
+      <c r="Z10" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" s="7" customFormat="1" ht="24" customHeight="1" thickBot="1">
+      <c r="A11" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="18"/>
+      <c r="Q11" s="18"/>
+      <c r="R11" s="18"/>
+      <c r="S11" s="18"/>
+      <c r="T11" s="18"/>
+      <c r="U11" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="V11" s="26"/>
+      <c r="W11" s="26"/>
+      <c r="X11" s="27"/>
+      <c r="Z11" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" s="7" customFormat="1" ht="24" customHeight="1">
+      <c r="A12" s="13"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="11"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="11"/>
+      <c r="T12" s="11"/>
+      <c r="U12" s="13"/>
+      <c r="V12" s="13"/>
+      <c r="W12" s="13"/>
+      <c r="X12" s="13"/>
+    </row>
+    <row r="13" spans="1:30" s="7" customFormat="1" ht="24" customHeight="1" thickBot="1">
+      <c r="A13" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20"/>
+      <c r="R13" s="20"/>
+      <c r="S13" s="20"/>
+      <c r="T13" s="20"/>
+      <c r="U13" s="20"/>
+      <c r="V13" s="20"/>
+      <c r="W13" s="20"/>
+      <c r="X13" s="20"/>
+    </row>
+    <row r="14" spans="1:30" s="7" customFormat="1" ht="24" customHeight="1">
+      <c r="A14" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="R7" s="39"/>
-      <c r="S7" s="39"/>
-      <c r="T7" s="39"/>
-      <c r="U7" s="39"/>
-      <c r="V7" s="39"/>
-      <c r="W7" s="39"/>
-      <c r="X7" s="41"/>
-      <c r="AC7" s="8"/>
-    </row>
-    <row r="8" spans="1:30" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A8" s="26"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
-      <c r="I8" s="27"/>
-      <c r="J8" s="27"/>
-      <c r="K8" s="27"/>
-      <c r="L8" s="27"/>
-      <c r="M8" s="27"/>
-      <c r="N8" s="27"/>
-      <c r="O8" s="27"/>
-      <c r="P8" s="27"/>
-      <c r="Q8" s="27"/>
-      <c r="R8" s="27"/>
-      <c r="S8" s="27"/>
-      <c r="T8" s="27"/>
-      <c r="U8" s="27"/>
-      <c r="V8" s="27"/>
-      <c r="W8" s="27"/>
-      <c r="X8" s="27"/>
-      <c r="AC8" s="8"/>
-    </row>
-    <row r="9" spans="1:30" s="7" customFormat="1" ht="24" customHeight="1" thickBot="1">
-      <c r="A9" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="15"/>
-      <c r="O9" s="15"/>
-      <c r="P9" s="15"/>
-      <c r="Q9" s="15"/>
-      <c r="R9" s="15"/>
-      <c r="S9" s="15"/>
-      <c r="T9" s="15"/>
-      <c r="U9" s="15"/>
-      <c r="V9" s="15"/>
-      <c r="W9" s="15"/>
-      <c r="X9" s="15"/>
-    </row>
-    <row r="10" spans="1:30" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A10" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="31"/>
-      <c r="K10" s="31"/>
-      <c r="L10" s="31"/>
-      <c r="M10" s="31"/>
-      <c r="N10" s="31"/>
-      <c r="O10" s="31"/>
-      <c r="P10" s="31"/>
-      <c r="Q10" s="31"/>
-      <c r="R10" s="31"/>
-      <c r="S10" s="31"/>
-      <c r="T10" s="31"/>
-      <c r="U10" s="31" t="s">
-        <v>56</v>
-      </c>
-      <c r="V10" s="31"/>
-      <c r="W10" s="31"/>
-      <c r="X10" s="32"/>
-      <c r="Z10" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:30" s="17" customFormat="1" ht="24" customHeight="1" thickBot="1">
-      <c r="A11" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="39" t="s">
-        <v>61</v>
-      </c>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="39"/>
-      <c r="J11" s="39"/>
-      <c r="K11" s="39"/>
-      <c r="L11" s="39"/>
-      <c r="M11" s="39"/>
-      <c r="N11" s="39"/>
-      <c r="O11" s="39"/>
-      <c r="P11" s="39"/>
-      <c r="Q11" s="39"/>
-      <c r="R11" s="39"/>
-      <c r="S11" s="39"/>
-      <c r="T11" s="39"/>
-      <c r="U11" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="V11" s="34"/>
-      <c r="W11" s="34"/>
-      <c r="X11" s="35"/>
-      <c r="Z11" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB11" s="16"/>
-      <c r="AC11" s="16"/>
-    </row>
-    <row r="12" spans="1:30" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="A12" s="24"/>
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="25"/>
-      <c r="I12" s="25"/>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="L12" s="25"/>
-      <c r="M12" s="25"/>
-      <c r="N12" s="25"/>
-      <c r="O12" s="25"/>
-      <c r="P12" s="25"/>
-      <c r="Q12" s="25"/>
-      <c r="R12" s="25"/>
-      <c r="S12" s="25"/>
-      <c r="T12" s="25"/>
-      <c r="U12" s="24"/>
-      <c r="V12" s="24"/>
-      <c r="W12" s="24"/>
-      <c r="X12" s="24"/>
-      <c r="AB12" s="16"/>
-      <c r="AC12" s="16"/>
-    </row>
-    <row r="13" spans="1:30" s="17" customFormat="1" ht="24" customHeight="1" thickBot="1">
-      <c r="A13" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="N13" s="15"/>
-      <c r="O13" s="15"/>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="15"/>
-      <c r="R13" s="15"/>
-      <c r="S13" s="15"/>
-      <c r="T13" s="15"/>
-      <c r="U13" s="15"/>
-      <c r="V13" s="15"/>
-      <c r="W13" s="15"/>
-      <c r="X13" s="15"/>
-      <c r="AB13" s="16"/>
-      <c r="AC13" s="16"/>
-    </row>
-    <row r="14" spans="1:30" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="A14" s="42" t="s">
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="29"/>
+      <c r="L14" s="30"/>
+      <c r="M14" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="B14" s="43"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="43"/>
-      <c r="L14" s="44"/>
-      <c r="M14" s="42" t="s">
-        <v>71</v>
-      </c>
-      <c r="N14" s="43"/>
-      <c r="O14" s="43"/>
-      <c r="P14" s="43"/>
-      <c r="Q14" s="43"/>
-      <c r="R14" s="43"/>
-      <c r="S14" s="43"/>
-      <c r="T14" s="43"/>
-      <c r="U14" s="43"/>
-      <c r="V14" s="43"/>
-      <c r="W14" s="43"/>
-      <c r="X14" s="51"/>
-    </row>
-    <row r="15" spans="1:30" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="A15" s="45"/>
-      <c r="B15" s="46"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46"/>
-      <c r="F15" s="46"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="46"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="46"/>
-      <c r="K15" s="46"/>
-      <c r="L15" s="47"/>
-      <c r="M15" s="45"/>
-      <c r="N15" s="46"/>
-      <c r="O15" s="46"/>
-      <c r="P15" s="46"/>
-      <c r="Q15" s="46"/>
-      <c r="R15" s="46"/>
-      <c r="S15" s="46"/>
-      <c r="T15" s="46"/>
-      <c r="U15" s="46"/>
-      <c r="V15" s="46"/>
-      <c r="W15" s="46"/>
-      <c r="X15" s="52"/>
-      <c r="AD15" s="22"/>
-    </row>
-    <row r="16" spans="1:30" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="A16" s="45"/>
-      <c r="B16" s="46"/>
-      <c r="C16" s="46"/>
-      <c r="D16" s="46"/>
-      <c r="E16" s="46"/>
-      <c r="F16" s="46"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="46"/>
-      <c r="I16" s="46"/>
-      <c r="J16" s="46"/>
-      <c r="K16" s="46"/>
-      <c r="L16" s="47"/>
-      <c r="M16" s="45"/>
-      <c r="N16" s="46"/>
-      <c r="O16" s="46"/>
-      <c r="P16" s="46"/>
-      <c r="Q16" s="46"/>
-      <c r="R16" s="46"/>
-      <c r="S16" s="46"/>
-      <c r="T16" s="46"/>
-      <c r="U16" s="46"/>
-      <c r="V16" s="46"/>
-      <c r="W16" s="46"/>
-      <c r="X16" s="52"/>
-      <c r="AD16" s="16"/>
-    </row>
-    <row r="17" spans="1:28" s="17" customFormat="1" ht="24" customHeight="1" thickBot="1">
-      <c r="A17" s="48"/>
-      <c r="B17" s="49"/>
-      <c r="C17" s="49"/>
-      <c r="D17" s="49"/>
-      <c r="E17" s="49"/>
-      <c r="F17" s="49"/>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49"/>
-      <c r="I17" s="49"/>
-      <c r="J17" s="49"/>
-      <c r="K17" s="49"/>
-      <c r="L17" s="50"/>
-      <c r="M17" s="48"/>
-      <c r="N17" s="49"/>
-      <c r="O17" s="49"/>
-      <c r="P17" s="49"/>
-      <c r="Q17" s="49"/>
-      <c r="R17" s="49"/>
-      <c r="S17" s="49"/>
-      <c r="T17" s="49"/>
-      <c r="U17" s="49"/>
-      <c r="V17" s="49"/>
-      <c r="W17" s="49"/>
-      <c r="X17" s="53"/>
-    </row>
-    <row r="18" spans="1:28" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="A18" s="21"/>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21"/>
-      <c r="M18" s="21"/>
-      <c r="N18" s="21"/>
-      <c r="O18" s="21"/>
-      <c r="P18" s="21"/>
-      <c r="Q18" s="21"/>
-      <c r="R18" s="21"/>
-      <c r="S18" s="21"/>
-      <c r="T18" s="21"/>
-      <c r="U18" s="21"/>
-      <c r="V18" s="21"/>
-      <c r="W18" s="21"/>
-      <c r="X18" s="21"/>
-    </row>
-    <row r="19" spans="1:28" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="A19" s="16"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="21"/>
-      <c r="N19" s="21"/>
-      <c r="O19" s="21"/>
-      <c r="P19" s="21"/>
-      <c r="Q19" s="21"/>
-      <c r="R19" s="21"/>
-      <c r="S19" s="21"/>
-      <c r="T19" s="21"/>
-      <c r="U19" s="21"/>
-      <c r="V19" s="21"/>
-      <c r="W19" s="21"/>
-      <c r="X19" s="21"/>
-    </row>
-    <row r="20" spans="1:28" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="A20" s="21"/>
-      <c r="B20" s="21"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="21"/>
-      <c r="J20" s="21"/>
-      <c r="K20" s="21"/>
-      <c r="L20" s="21"/>
-      <c r="M20" s="21"/>
-      <c r="N20" s="21"/>
-      <c r="O20" s="21"/>
-      <c r="P20" s="21"/>
-      <c r="Q20" s="21"/>
-      <c r="R20" s="21"/>
-      <c r="S20" s="21"/>
-      <c r="T20" s="21"/>
-      <c r="U20" s="21"/>
-      <c r="V20" s="21"/>
-      <c r="W20" s="21"/>
-      <c r="X20" s="21"/>
-    </row>
-    <row r="21" spans="1:28" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="A21" s="21"/>
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="21"/>
-      <c r="K21" s="21"/>
-      <c r="L21" s="21"/>
-      <c r="M21" s="21"/>
-      <c r="N21" s="21"/>
-      <c r="O21" s="21"/>
-      <c r="P21" s="21"/>
-      <c r="Q21" s="21"/>
-      <c r="R21" s="21"/>
-      <c r="S21" s="21"/>
-      <c r="T21" s="21"/>
-      <c r="U21" s="21"/>
-      <c r="V21" s="21"/>
-      <c r="W21" s="21"/>
-      <c r="X21" s="21"/>
-    </row>
-    <row r="22" spans="1:28" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="A22" s="21"/>
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="21"/>
-      <c r="K22" s="21"/>
-      <c r="L22" s="21"/>
-      <c r="M22" s="21"/>
-      <c r="N22" s="21"/>
-      <c r="O22" s="21"/>
-      <c r="P22" s="21"/>
-      <c r="Q22" s="21"/>
-      <c r="R22" s="21"/>
-      <c r="S22" s="21"/>
-      <c r="T22" s="21"/>
-      <c r="U22" s="21"/>
-      <c r="V22" s="21"/>
-      <c r="W22" s="21"/>
-      <c r="X22" s="21"/>
-    </row>
-    <row r="23" spans="1:28" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="A23" s="21"/>
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="21"/>
-      <c r="K23" s="21"/>
-      <c r="L23" s="21"/>
-      <c r="M23" s="21"/>
-      <c r="N23" s="21"/>
-      <c r="O23" s="21"/>
-      <c r="P23" s="21"/>
-      <c r="Q23" s="21"/>
-      <c r="R23" s="21"/>
-      <c r="S23" s="21"/>
-      <c r="T23" s="21"/>
-      <c r="U23" s="21"/>
-      <c r="V23" s="21"/>
-      <c r="W23" s="21"/>
-      <c r="X23" s="21"/>
-    </row>
-    <row r="24" spans="1:28" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="A24" s="21"/>
-      <c r="B24" s="21"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="21"/>
-      <c r="I24" s="21"/>
-      <c r="J24" s="21"/>
-      <c r="K24" s="21"/>
-      <c r="L24" s="21"/>
-      <c r="M24" s="21"/>
-      <c r="N24" s="21"/>
-      <c r="O24" s="21"/>
-      <c r="P24" s="21"/>
-      <c r="Q24" s="21"/>
-      <c r="R24" s="21"/>
-      <c r="S24" s="21"/>
-      <c r="T24" s="21"/>
-      <c r="U24" s="21"/>
-      <c r="V24" s="21"/>
-      <c r="W24" s="21"/>
-      <c r="X24" s="21"/>
-    </row>
-    <row r="25" spans="1:28" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="M25" s="21"/>
-      <c r="N25" s="21"/>
-      <c r="O25" s="21"/>
-      <c r="P25" s="21"/>
-      <c r="Q25" s="21"/>
-      <c r="R25" s="21"/>
-      <c r="S25" s="21"/>
-      <c r="T25" s="21"/>
-      <c r="U25" s="21"/>
-      <c r="V25" s="21"/>
-      <c r="W25" s="21"/>
-      <c r="X25" s="21"/>
-      <c r="AB25" s="33"/>
-    </row>
-    <row r="26" spans="1:28" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="M26" s="21"/>
-      <c r="N26" s="21"/>
-      <c r="O26" s="21"/>
-      <c r="P26" s="21"/>
-      <c r="Q26" s="21"/>
-      <c r="R26" s="21"/>
-      <c r="S26" s="21"/>
-      <c r="T26" s="21"/>
-      <c r="U26" s="21"/>
-      <c r="V26" s="21"/>
-      <c r="W26" s="21"/>
-      <c r="X26" s="21"/>
-    </row>
-    <row r="27" spans="1:28" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="M27" s="21"/>
-      <c r="N27" s="21"/>
-      <c r="O27" s="21"/>
-      <c r="P27" s="21"/>
-      <c r="Q27" s="21"/>
-      <c r="R27" s="21"/>
-      <c r="S27" s="21"/>
-      <c r="T27" s="21"/>
-      <c r="U27" s="21"/>
-      <c r="V27" s="21"/>
-      <c r="W27" s="21"/>
-      <c r="X27" s="21"/>
-    </row>
-    <row r="28" spans="1:28" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="M28" s="21"/>
-      <c r="N28" s="21"/>
-      <c r="O28" s="21"/>
-      <c r="P28" s="21"/>
-      <c r="Q28" s="21"/>
-      <c r="R28" s="21"/>
-      <c r="S28" s="21"/>
-      <c r="T28" s="21"/>
-      <c r="U28" s="21"/>
-      <c r="V28" s="21"/>
-      <c r="W28" s="21"/>
-      <c r="X28" s="21"/>
-    </row>
-    <row r="29" spans="1:28" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="M29" s="21"/>
-      <c r="N29" s="21"/>
-      <c r="O29" s="21"/>
-      <c r="P29" s="21"/>
-      <c r="Q29" s="21"/>
-      <c r="R29" s="21"/>
-      <c r="S29" s="21"/>
-      <c r="T29" s="21"/>
-      <c r="U29" s="21"/>
-      <c r="V29" s="21"/>
-      <c r="W29" s="21"/>
-      <c r="X29" s="21"/>
-    </row>
-    <row r="30" spans="1:28" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="M30" s="21"/>
-      <c r="N30" s="21"/>
-      <c r="O30" s="21"/>
-      <c r="P30" s="21"/>
-      <c r="Q30" s="21"/>
-      <c r="R30" s="21"/>
-      <c r="S30" s="21"/>
-      <c r="T30" s="21"/>
-      <c r="U30" s="21"/>
-      <c r="V30" s="21"/>
-      <c r="W30" s="21"/>
-      <c r="X30" s="21"/>
-    </row>
-    <row r="31" spans="1:28" s="17" customFormat="1" ht="24" customHeight="1"/>
-    <row r="32" spans="1:28" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="A32" s="16"/>
-      <c r="B32" s="16"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16"/>
-      <c r="I32" s="16"/>
-      <c r="J32" s="16"/>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="16"/>
-      <c r="O32" s="16"/>
-      <c r="P32" s="16"/>
-      <c r="Q32" s="16"/>
-      <c r="R32" s="16"/>
-      <c r="S32" s="16"/>
-      <c r="T32" s="16"/>
-      <c r="U32" s="16"/>
-      <c r="V32" s="16"/>
-      <c r="W32" s="16"/>
-      <c r="X32" s="16"/>
-    </row>
-    <row r="33" spans="1:26" s="17" customFormat="1" ht="24" customHeight="1">
-      <c r="A33" s="20"/>
-      <c r="B33" s="20"/>
-      <c r="C33" s="20"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="20"/>
-      <c r="I33" s="20"/>
-      <c r="J33" s="20"/>
-      <c r="K33" s="20"/>
-      <c r="L33" s="20"/>
-      <c r="M33" s="20"/>
-      <c r="N33" s="20"/>
-      <c r="O33" s="20"/>
-      <c r="P33" s="20"/>
-      <c r="Q33" s="20"/>
-      <c r="R33" s="20"/>
-      <c r="S33" s="20"/>
-      <c r="T33" s="20"/>
-      <c r="U33" s="20"/>
-      <c r="V33" s="20"/>
-      <c r="W33" s="20"/>
-      <c r="X33" s="20"/>
-      <c r="Z33" s="23"/>
-    </row>
-    <row r="34" spans="1:26" s="17" customFormat="1" ht="24" customHeight="1"/>
-    <row r="35" spans="1:26" s="17" customFormat="1" ht="24" customHeight="1"/>
-    <row r="36" spans="1:26" s="17" customFormat="1" ht="24" customHeight="1"/>
-    <row r="37" spans="1:26" s="17" customFormat="1" ht="24" customHeight="1"/>
-    <row r="38" spans="1:26" s="17" customFormat="1" ht="24" customHeight="1"/>
-    <row r="39" spans="1:26" s="17" customFormat="1" ht="24" customHeight="1"/>
-    <row r="40" spans="1:26" s="17" customFormat="1" ht="24" customHeight="1"/>
-    <row r="41" spans="1:26" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A41" s="17"/>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="17"/>
-      <c r="G41" s="17"/>
-      <c r="H41" s="17"/>
-      <c r="I41" s="17"/>
-      <c r="J41" s="17"/>
-      <c r="K41" s="17"/>
-      <c r="L41" s="17"/>
-      <c r="M41" s="17"/>
-      <c r="N41" s="17"/>
-      <c r="O41" s="17"/>
-      <c r="P41" s="17"/>
-      <c r="Q41" s="17"/>
-      <c r="R41" s="17"/>
-      <c r="S41" s="17"/>
-      <c r="T41" s="17"/>
-      <c r="U41" s="17"/>
-      <c r="V41" s="17"/>
-      <c r="W41" s="17"/>
-      <c r="X41" s="17"/>
-    </row>
-    <row r="42" spans="1:26" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A42" s="17"/>
-      <c r="B42" s="17"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="17"/>
-      <c r="G42" s="17"/>
-      <c r="H42" s="17"/>
-      <c r="I42" s="17"/>
-      <c r="J42" s="17"/>
-      <c r="K42" s="17"/>
-      <c r="L42" s="17"/>
-      <c r="M42" s="17"/>
-      <c r="N42" s="17"/>
-      <c r="O42" s="17"/>
-      <c r="P42" s="17"/>
-      <c r="Q42" s="17"/>
-      <c r="R42" s="17"/>
-      <c r="S42" s="17"/>
-      <c r="T42" s="17"/>
-      <c r="U42" s="17"/>
-      <c r="V42" s="17"/>
-      <c r="W42" s="17"/>
-      <c r="X42" s="17"/>
+      <c r="N14" s="29"/>
+      <c r="O14" s="29"/>
+      <c r="P14" s="29"/>
+      <c r="Q14" s="29"/>
+      <c r="R14" s="29"/>
+      <c r="S14" s="29"/>
+      <c r="T14" s="29"/>
+      <c r="U14" s="29"/>
+      <c r="V14" s="29"/>
+      <c r="W14" s="29"/>
+      <c r="X14" s="37"/>
+    </row>
+    <row r="15" spans="1:30" s="7" customFormat="1" ht="24" customHeight="1">
+      <c r="A15" s="31"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="33"/>
+      <c r="M15" s="31"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
+      <c r="T15" s="32"/>
+      <c r="U15" s="32"/>
+      <c r="V15" s="32"/>
+      <c r="W15" s="32"/>
+      <c r="X15" s="38"/>
+      <c r="AD15" s="11"/>
+    </row>
+    <row r="16" spans="1:30" s="7" customFormat="1" ht="24" customHeight="1">
+      <c r="A16" s="31"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="32"/>
+      <c r="K16" s="32"/>
+      <c r="L16" s="33"/>
+      <c r="M16" s="31"/>
+      <c r="N16" s="32"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="32"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="32"/>
+      <c r="S16" s="32"/>
+      <c r="T16" s="32"/>
+      <c r="U16" s="32"/>
+      <c r="V16" s="32"/>
+      <c r="W16" s="32"/>
+      <c r="X16" s="38"/>
+    </row>
+    <row r="17" spans="1:28" s="7" customFormat="1" ht="24" customHeight="1" thickBot="1">
+      <c r="A17" s="34"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="35"/>
+      <c r="K17" s="35"/>
+      <c r="L17" s="36"/>
+      <c r="M17" s="34"/>
+      <c r="N17" s="35"/>
+      <c r="O17" s="35"/>
+      <c r="P17" s="35"/>
+      <c r="Q17" s="35"/>
+      <c r="R17" s="35"/>
+      <c r="S17" s="35"/>
+      <c r="T17" s="35"/>
+      <c r="U17" s="35"/>
+      <c r="V17" s="35"/>
+      <c r="W17" s="35"/>
+      <c r="X17" s="39"/>
+    </row>
+    <row r="18" spans="1:28" s="7" customFormat="1" ht="24" customHeight="1">
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="10"/>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="10"/>
+      <c r="S18" s="10"/>
+      <c r="T18" s="10"/>
+      <c r="U18" s="10"/>
+      <c r="V18" s="10"/>
+      <c r="W18" s="10"/>
+      <c r="X18" s="10"/>
+    </row>
+    <row r="19" spans="1:28" s="7" customFormat="1" ht="24" customHeight="1">
+      <c r="M19" s="10"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="10"/>
+      <c r="P19" s="10"/>
+      <c r="Q19" s="10"/>
+      <c r="R19" s="10"/>
+      <c r="S19" s="10"/>
+      <c r="T19" s="10"/>
+      <c r="U19" s="10"/>
+      <c r="V19" s="10"/>
+      <c r="W19" s="10"/>
+      <c r="X19" s="10"/>
+    </row>
+    <row r="20" spans="1:28" s="7" customFormat="1" ht="24" customHeight="1">
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="10"/>
+      <c r="S20" s="10"/>
+      <c r="T20" s="10"/>
+      <c r="U20" s="10"/>
+      <c r="V20" s="10"/>
+      <c r="W20" s="10"/>
+      <c r="X20" s="10"/>
+    </row>
+    <row r="21" spans="1:28" s="7" customFormat="1" ht="24" customHeight="1">
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="10"/>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="10"/>
+      <c r="R21" s="10"/>
+      <c r="S21" s="10"/>
+      <c r="T21" s="10"/>
+      <c r="U21" s="10"/>
+      <c r="V21" s="10"/>
+      <c r="W21" s="10"/>
+      <c r="X21" s="10"/>
+    </row>
+    <row r="22" spans="1:28" s="7" customFormat="1" ht="24" customHeight="1">
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="10"/>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="10"/>
+      <c r="R22" s="10"/>
+      <c r="S22" s="10"/>
+      <c r="T22" s="10"/>
+      <c r="U22" s="10"/>
+      <c r="V22" s="10"/>
+      <c r="W22" s="10"/>
+      <c r="X22" s="10"/>
+    </row>
+    <row r="23" spans="1:28" s="7" customFormat="1" ht="24" customHeight="1">
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="10"/>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="10"/>
+      <c r="R23" s="10"/>
+      <c r="S23" s="10"/>
+      <c r="T23" s="10"/>
+      <c r="U23" s="10"/>
+      <c r="V23" s="10"/>
+      <c r="W23" s="10"/>
+      <c r="X23" s="10"/>
+    </row>
+    <row r="24" spans="1:28" s="7" customFormat="1" ht="24" customHeight="1">
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="10"/>
+      <c r="P24" s="10"/>
+      <c r="Q24" s="10"/>
+      <c r="R24" s="10"/>
+      <c r="S24" s="10"/>
+      <c r="T24" s="10"/>
+      <c r="U24" s="10"/>
+      <c r="V24" s="10"/>
+      <c r="W24" s="10"/>
+      <c r="X24" s="10"/>
+    </row>
+    <row r="25" spans="1:28" s="7" customFormat="1" ht="24" customHeight="1">
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="10"/>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="10"/>
+      <c r="R25" s="10"/>
+      <c r="S25" s="10"/>
+      <c r="T25" s="10"/>
+      <c r="U25" s="10"/>
+      <c r="V25" s="10"/>
+      <c r="W25" s="10"/>
+      <c r="X25" s="10"/>
+      <c r="AB25" s="14"/>
+    </row>
+    <row r="26" spans="1:28" s="7" customFormat="1" ht="24" customHeight="1">
+      <c r="M26" s="10"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="10"/>
+      <c r="P26" s="10"/>
+      <c r="Q26" s="10"/>
+      <c r="R26" s="10"/>
+      <c r="S26" s="10"/>
+      <c r="T26" s="10"/>
+      <c r="U26" s="10"/>
+      <c r="V26" s="10"/>
+      <c r="W26" s="10"/>
+      <c r="X26" s="10"/>
+    </row>
+    <row r="27" spans="1:28" s="7" customFormat="1" ht="24" customHeight="1">
+      <c r="M27" s="10"/>
+      <c r="N27" s="10"/>
+      <c r="O27" s="10"/>
+      <c r="P27" s="10"/>
+      <c r="Q27" s="10"/>
+      <c r="R27" s="10"/>
+      <c r="S27" s="10"/>
+      <c r="T27" s="10"/>
+      <c r="U27" s="10"/>
+      <c r="V27" s="10"/>
+      <c r="W27" s="10"/>
+      <c r="X27" s="10"/>
+    </row>
+    <row r="28" spans="1:28" s="7" customFormat="1" ht="24" customHeight="1">
+      <c r="M28" s="10"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="10"/>
+      <c r="P28" s="10"/>
+      <c r="Q28" s="10"/>
+      <c r="R28" s="10"/>
+      <c r="S28" s="10"/>
+      <c r="T28" s="10"/>
+      <c r="U28" s="10"/>
+      <c r="V28" s="10"/>
+      <c r="W28" s="10"/>
+      <c r="X28" s="10"/>
+    </row>
+    <row r="29" spans="1:28" s="7" customFormat="1" ht="24" customHeight="1">
+      <c r="M29" s="10"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="10"/>
+      <c r="P29" s="10"/>
+      <c r="Q29" s="10"/>
+      <c r="R29" s="10"/>
+      <c r="S29" s="10"/>
+      <c r="T29" s="10"/>
+      <c r="U29" s="10"/>
+      <c r="V29" s="10"/>
+      <c r="W29" s="10"/>
+      <c r="X29" s="10"/>
+    </row>
+    <row r="30" spans="1:28" s="7" customFormat="1" ht="24" customHeight="1">
+      <c r="M30" s="10"/>
+      <c r="N30" s="10"/>
+      <c r="O30" s="10"/>
+      <c r="P30" s="10"/>
+      <c r="Q30" s="10"/>
+      <c r="R30" s="10"/>
+      <c r="S30" s="10"/>
+      <c r="T30" s="10"/>
+      <c r="U30" s="10"/>
+      <c r="V30" s="10"/>
+      <c r="W30" s="10"/>
+      <c r="X30" s="10"/>
+    </row>
+    <row r="31" spans="1:28" s="7" customFormat="1" ht="24" customHeight="1"/>
+    <row r="32" spans="1:28" s="7" customFormat="1" ht="24" customHeight="1"/>
+    <row r="33" spans="1:26" s="7" customFormat="1" ht="24" customHeight="1">
+      <c r="A33" s="9"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9"/>
+      <c r="M33" s="9"/>
+      <c r="N33" s="9"/>
+      <c r="O33" s="9"/>
+      <c r="P33" s="9"/>
+      <c r="Q33" s="9"/>
+      <c r="R33" s="9"/>
+      <c r="S33" s="9"/>
+      <c r="T33" s="9"/>
+      <c r="U33" s="9"/>
+      <c r="V33" s="9"/>
+      <c r="W33" s="9"/>
+      <c r="X33" s="9"/>
+      <c r="Z33" s="12"/>
+    </row>
+    <row r="34" spans="1:26" s="7" customFormat="1" ht="24" customHeight="1"/>
+    <row r="35" spans="1:26" s="7" customFormat="1" ht="24" customHeight="1"/>
+    <row r="36" spans="1:26" s="7" customFormat="1" ht="24" customHeight="1"/>
+    <row r="37" spans="1:26" s="7" customFormat="1" ht="24" customHeight="1"/>
+    <row r="38" spans="1:26" s="7" customFormat="1" ht="24" customHeight="1"/>
+    <row r="39" spans="1:26" s="7" customFormat="1" ht="24" customHeight="1"/>
+    <row r="40" spans="1:26" s="7" customFormat="1" ht="24" customHeight="1"/>
+    <row r="41" spans="1:26" s="6" customFormat="1" ht="24" customHeight="1">
+      <c r="A41" s="7"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
+      <c r="H41" s="7"/>
+      <c r="I41" s="7"/>
+      <c r="J41" s="7"/>
+      <c r="K41" s="7"/>
+      <c r="L41" s="7"/>
+      <c r="M41" s="7"/>
+      <c r="N41" s="7"/>
+      <c r="O41" s="7"/>
+      <c r="P41" s="7"/>
+      <c r="Q41" s="7"/>
+      <c r="R41" s="7"/>
+      <c r="S41" s="7"/>
+      <c r="T41" s="7"/>
+      <c r="U41" s="7"/>
+      <c r="V41" s="7"/>
+      <c r="W41" s="7"/>
+      <c r="X41" s="7"/>
+    </row>
+    <row r="42" spans="1:26" s="6" customFormat="1" ht="24" customHeight="1">
+      <c r="A42" s="7"/>
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
+      <c r="H42" s="7"/>
+      <c r="I42" s="7"/>
+      <c r="J42" s="7"/>
+      <c r="K42" s="7"/>
+      <c r="L42" s="7"/>
+      <c r="M42" s="7"/>
+      <c r="N42" s="7"/>
+      <c r="O42" s="7"/>
+      <c r="P42" s="7"/>
+      <c r="Q42" s="7"/>
+      <c r="R42" s="7"/>
+      <c r="S42" s="7"/>
+      <c r="T42" s="7"/>
+      <c r="U42" s="7"/>
+      <c r="V42" s="7"/>
+      <c r="W42" s="7"/>
+      <c r="X42" s="7"/>
     </row>
     <row r="43" spans="1:26" ht="24" customHeight="1">
-      <c r="A43" s="20"/>
-      <c r="B43" s="20"/>
-      <c r="C43" s="20"/>
-      <c r="D43" s="20"/>
-      <c r="E43" s="20"/>
-      <c r="F43" s="20"/>
-      <c r="G43" s="20"/>
-      <c r="H43" s="20"/>
-      <c r="I43" s="20"/>
-      <c r="J43" s="20"/>
-      <c r="K43" s="20"/>
-      <c r="L43" s="20"/>
-      <c r="M43" s="20"/>
-      <c r="N43" s="20"/>
-      <c r="O43" s="20"/>
-      <c r="P43" s="20"/>
-      <c r="Q43" s="20"/>
-      <c r="R43" s="20"/>
-      <c r="S43" s="20"/>
-      <c r="T43" s="20"/>
-      <c r="U43" s="20"/>
-      <c r="V43" s="20"/>
-      <c r="W43" s="20"/>
-      <c r="X43" s="20"/>
+      <c r="A43" s="9"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
+      <c r="J43" s="9"/>
+      <c r="K43" s="9"/>
+      <c r="L43" s="9"/>
+      <c r="M43" s="9"/>
+      <c r="N43" s="9"/>
+      <c r="O43" s="9"/>
+      <c r="P43" s="9"/>
+      <c r="Q43" s="9"/>
+      <c r="R43" s="9"/>
+      <c r="S43" s="9"/>
+      <c r="T43" s="9"/>
+      <c r="U43" s="9"/>
+      <c r="V43" s="9"/>
+      <c r="W43" s="9"/>
+      <c r="X43" s="9"/>
       <c r="Z43" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="Q6:X6"/>
-    <mergeCell ref="M7:P7"/>
-    <mergeCell ref="Q7:X7"/>
-    <mergeCell ref="A9:X9"/>
-    <mergeCell ref="A3:X3"/>
-    <mergeCell ref="E4:X4"/>
-    <mergeCell ref="M5:P5"/>
-    <mergeCell ref="Q5:X5"/>
-    <mergeCell ref="M6:P6"/>
-    <mergeCell ref="E10:T10"/>
-    <mergeCell ref="U10:X10"/>
-    <mergeCell ref="E11:T11"/>
-    <mergeCell ref="U11:X11"/>
-    <mergeCell ref="A13:L13"/>
-    <mergeCell ref="M13:X13"/>
+    <mergeCell ref="F1:S2"/>
+    <mergeCell ref="A1:E2"/>
     <mergeCell ref="A14:L17"/>
     <mergeCell ref="M14:X17"/>
     <mergeCell ref="A11:D11"/>
@@ -2067,8 +1992,21 @@
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="E7:L7"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="F1:S2"/>
-    <mergeCell ref="A1:E2"/>
+    <mergeCell ref="E10:T10"/>
+    <mergeCell ref="U10:X10"/>
+    <mergeCell ref="E11:T11"/>
+    <mergeCell ref="U11:X11"/>
+    <mergeCell ref="A13:L13"/>
+    <mergeCell ref="M13:X13"/>
+    <mergeCell ref="Q6:X6"/>
+    <mergeCell ref="M7:P7"/>
+    <mergeCell ref="Q7:X7"/>
+    <mergeCell ref="A9:X9"/>
+    <mergeCell ref="A3:X3"/>
+    <mergeCell ref="E4:X4"/>
+    <mergeCell ref="M5:P5"/>
+    <mergeCell ref="Q5:X5"/>
+    <mergeCell ref="M6:P6"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="1">
@@ -2084,7 +2022,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -2116,7 +2054,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="20">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -2124,7 +2062,7 @@
         <v>48</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -2133,7 +2071,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="20">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -2141,13 +2079,13 @@
         <v>49</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="20">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -2161,7 +2099,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="20">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>51</v>
       </c>
@@ -2175,7 +2113,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="20">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>52</v>
       </c>
@@ -2189,7 +2127,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="20">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>53</v>
       </c>
@@ -2203,9 +2141,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="20">
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B9" t="s">
         <v>54</v>
@@ -2217,7 +2155,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="20">
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>55</v>
       </c>
@@ -2231,10 +2169,10 @@
         <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="20">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>59</v>
       </c>
@@ -2248,10 +2186,10 @@
         <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="20">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>56</v>
       </c>
@@ -2259,79 +2197,45 @@
         <v>56</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
         <v>10</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="20">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B13" t="s">
         <v>57</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="20">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B14" t="s">
         <v>58</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="20">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="20"/>
-    <row r="17" ht="20"/>
-    <row r="18" ht="20"/>
-    <row r="19" ht="20"/>
-    <row r="20" ht="20"/>
-    <row r="21" ht="20"/>
-    <row r="22" ht="20"/>
-    <row r="23" ht="20"/>
-    <row r="24" ht="20"/>
-    <row r="25" ht="20"/>
-    <row r="26" ht="20"/>
-    <row r="27" ht="20"/>
-    <row r="28" ht="20"/>
-    <row r="29" ht="20"/>
-    <row r="30" ht="20"/>
-    <row r="31" ht="20"/>
-    <row r="32" ht="20"/>
-    <row r="33" ht="20"/>
-    <row r="34" ht="20"/>
-    <row r="35" ht="20"/>
-    <row r="36" ht="20"/>
-    <row r="37" ht="20"/>
-    <row r="38" ht="20"/>
-    <row r="39" ht="20"/>
-    <row r="40" ht="20"/>
-    <row r="41" ht="20"/>
-    <row r="42" ht="20"/>
-    <row r="43" ht="20"/>
-    <row r="44" ht="20"/>
-    <row r="45" ht="20"/>
-    <row r="46" ht="20"/>
-    <row r="47" ht="20"/>
-    <row r="48" ht="20"/>
-    <row r="49" ht="20"/>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">

--- a/public/kk-gabji.xlsx
+++ b/public/kk-gabji.xlsx
@@ -3,21 +3,34 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10802"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09CB0C87-BC95-5E4E-BCC5-DB48C5026463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD2033C2-27F7-084E-8A94-2BC379DE51E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19200" yWindow="600" windowWidth="19200" windowHeight="19140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="양식" sheetId="1" r:id="rId1"/>
     <sheet name="필드" sheetId="2" r:id="rId2"/>
     <sheet name="안내" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="82">
   <si>
     <t>{{발행처로고}}</t>
   </si>
@@ -295,6 +308,9 @@
   <si>
     <t>{{부속비고}}</t>
     <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>꼬리말</t>
   </si>
 </sst>
 </file>
@@ -651,107 +667,107 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1100,29 +1116,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="24" customHeight="1">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="47" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="47"/>
-      <c r="P1" s="47"/>
-      <c r="Q1" s="47"/>
-      <c r="R1" s="47"/>
-      <c r="S1" s="47"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
+      <c r="S1" s="15"/>
       <c r="T1" s="8"/>
       <c r="U1" s="8"/>
       <c r="V1" s="8"/>
@@ -1133,25 +1149,25 @@
       </c>
     </row>
     <row r="2" spans="1:30" ht="24" customHeight="1">
-      <c r="A2" s="48"/>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
-      <c r="L2" s="47"/>
-      <c r="M2" s="47"/>
-      <c r="N2" s="47"/>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
       <c r="T2" s="8"/>
       <c r="U2" s="8"/>
       <c r="V2" s="8"/>
@@ -1159,164 +1175,164 @@
       <c r="X2" s="8"/>
     </row>
     <row r="3" spans="1:30" s="6" customFormat="1" ht="24" customHeight="1" thickBot="1">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="20"/>
-      <c r="L3" s="20"/>
-      <c r="M3" s="20"/>
-      <c r="N3" s="20"/>
-      <c r="O3" s="20"/>
-      <c r="P3" s="20"/>
-      <c r="Q3" s="20"/>
-      <c r="R3" s="20"/>
-      <c r="S3" s="20"/>
-      <c r="T3" s="20"/>
-      <c r="U3" s="20"/>
-      <c r="V3" s="20"/>
-      <c r="W3" s="20"/>
-      <c r="X3" s="20"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="42"/>
+      <c r="N3" s="42"/>
+      <c r="O3" s="42"/>
+      <c r="P3" s="42"/>
+      <c r="Q3" s="42"/>
+      <c r="R3" s="42"/>
+      <c r="S3" s="42"/>
+      <c r="T3" s="42"/>
+      <c r="U3" s="42"/>
+      <c r="V3" s="42"/>
+      <c r="W3" s="42"/>
+      <c r="X3" s="42"/>
     </row>
     <row r="4" spans="1:30" s="6" customFormat="1" ht="24" customHeight="1">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="21" t="s">
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
-      <c r="N4" s="21"/>
-      <c r="O4" s="21"/>
-      <c r="P4" s="21"/>
-      <c r="Q4" s="21"/>
-      <c r="R4" s="21"/>
-      <c r="S4" s="21"/>
-      <c r="T4" s="21"/>
-      <c r="U4" s="21"/>
-      <c r="V4" s="21"/>
-      <c r="W4" s="21"/>
-      <c r="X4" s="22"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
+      <c r="K4" s="45"/>
+      <c r="L4" s="45"/>
+      <c r="M4" s="45"/>
+      <c r="N4" s="45"/>
+      <c r="O4" s="45"/>
+      <c r="P4" s="45"/>
+      <c r="Q4" s="45"/>
+      <c r="R4" s="45"/>
+      <c r="S4" s="45"/>
+      <c r="T4" s="45"/>
+      <c r="U4" s="45"/>
+      <c r="V4" s="45"/>
+      <c r="W4" s="45"/>
+      <c r="X4" s="46"/>
     </row>
     <row r="5" spans="1:30" s="6" customFormat="1" ht="24" customHeight="1">
-      <c r="A5" s="44" t="s">
+      <c r="A5" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="15" t="s">
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="23" t="s">
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="35"/>
+      <c r="L5" s="35"/>
+      <c r="M5" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="N5" s="23"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="15" t="s">
+      <c r="N5" s="34"/>
+      <c r="O5" s="34"/>
+      <c r="P5" s="34"/>
+      <c r="Q5" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="R5" s="15"/>
-      <c r="S5" s="15"/>
-      <c r="T5" s="15"/>
-      <c r="U5" s="15"/>
-      <c r="V5" s="15"/>
-      <c r="W5" s="15"/>
-      <c r="X5" s="16"/>
+      <c r="R5" s="35"/>
+      <c r="S5" s="35"/>
+      <c r="T5" s="35"/>
+      <c r="U5" s="35"/>
+      <c r="V5" s="35"/>
+      <c r="W5" s="35"/>
+      <c r="X5" s="43"/>
     </row>
     <row r="6" spans="1:30" s="6" customFormat="1" ht="24" customHeight="1">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="15" t="s">
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="23" t="s">
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="35"/>
+      <c r="L6" s="35"/>
+      <c r="M6" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="15" t="s">
+      <c r="N6" s="34"/>
+      <c r="O6" s="34"/>
+      <c r="P6" s="34"/>
+      <c r="Q6" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="R6" s="15"/>
-      <c r="S6" s="15"/>
-      <c r="T6" s="15"/>
-      <c r="U6" s="15"/>
-      <c r="V6" s="15"/>
-      <c r="W6" s="15"/>
-      <c r="X6" s="16"/>
+      <c r="R6" s="35"/>
+      <c r="S6" s="35"/>
+      <c r="T6" s="35"/>
+      <c r="U6" s="35"/>
+      <c r="V6" s="35"/>
+      <c r="W6" s="35"/>
+      <c r="X6" s="43"/>
     </row>
     <row r="7" spans="1:30" s="6" customFormat="1" ht="24" customHeight="1" thickBot="1">
-      <c r="A7" s="45" t="s">
+      <c r="A7" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="18" t="s">
+      <c r="B7" s="37"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="37"/>
+      <c r="E7" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="18"/>
-      <c r="L7" s="18"/>
-      <c r="M7" s="17" t="s">
+      <c r="F7" s="38"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="38"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="L7" s="38"/>
+      <c r="M7" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="N7" s="17"/>
-      <c r="O7" s="17"/>
-      <c r="P7" s="17"/>
-      <c r="Q7" s="18" t="s">
+      <c r="N7" s="37"/>
+      <c r="O7" s="37"/>
+      <c r="P7" s="37"/>
+      <c r="Q7" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="R7" s="18"/>
-      <c r="S7" s="18"/>
-      <c r="T7" s="18"/>
-      <c r="U7" s="18"/>
-      <c r="V7" s="18"/>
-      <c r="W7" s="18"/>
-      <c r="X7" s="19"/>
+      <c r="R7" s="38"/>
+      <c r="S7" s="38"/>
+      <c r="T7" s="38"/>
+      <c r="U7" s="38"/>
+      <c r="V7" s="38"/>
+      <c r="W7" s="38"/>
+      <c r="X7" s="44"/>
     </row>
     <row r="8" spans="1:30" s="6" customFormat="1" ht="24" customHeight="1">
       <c r="A8" s="11"/>
@@ -1345,99 +1361,99 @@
       <c r="X8" s="7"/>
     </row>
     <row r="9" spans="1:30" s="6" customFormat="1" ht="24" customHeight="1" thickBot="1">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="20"/>
-      <c r="O9" s="20"/>
-      <c r="P9" s="20"/>
-      <c r="Q9" s="20"/>
-      <c r="R9" s="20"/>
-      <c r="S9" s="20"/>
-      <c r="T9" s="20"/>
-      <c r="U9" s="20"/>
-      <c r="V9" s="20"/>
-      <c r="W9" s="20"/>
-      <c r="X9" s="20"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="42"/>
+      <c r="L9" s="42"/>
+      <c r="M9" s="42"/>
+      <c r="N9" s="42"/>
+      <c r="O9" s="42"/>
+      <c r="P9" s="42"/>
+      <c r="Q9" s="42"/>
+      <c r="R9" s="42"/>
+      <c r="S9" s="42"/>
+      <c r="T9" s="42"/>
+      <c r="U9" s="42"/>
+      <c r="V9" s="42"/>
+      <c r="W9" s="42"/>
+      <c r="X9" s="42"/>
     </row>
     <row r="10" spans="1:30" s="6" customFormat="1" ht="24" customHeight="1">
-      <c r="A10" s="46" t="s">
+      <c r="A10" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="24"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24" t="s">
+      <c r="B10" s="40"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="24"/>
-      <c r="M10" s="24"/>
-      <c r="N10" s="24"/>
-      <c r="O10" s="24"/>
-      <c r="P10" s="24"/>
-      <c r="Q10" s="24"/>
-      <c r="R10" s="24"/>
-      <c r="S10" s="24"/>
-      <c r="T10" s="24"/>
-      <c r="U10" s="24" t="s">
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="40"/>
+      <c r="M10" s="40"/>
+      <c r="N10" s="40"/>
+      <c r="O10" s="40"/>
+      <c r="P10" s="40"/>
+      <c r="Q10" s="40"/>
+      <c r="R10" s="40"/>
+      <c r="S10" s="40"/>
+      <c r="T10" s="40"/>
+      <c r="U10" s="40" t="s">
         <v>56</v>
       </c>
-      <c r="V10" s="24"/>
-      <c r="W10" s="24"/>
-      <c r="X10" s="25"/>
+      <c r="V10" s="40"/>
+      <c r="W10" s="40"/>
+      <c r="X10" s="41"/>
       <c r="Z10" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:30" s="7" customFormat="1" ht="24" customHeight="1" thickBot="1">
-      <c r="A11" s="40" t="s">
+      <c r="A11" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="41"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="18" t="s">
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="18"/>
-      <c r="M11" s="18"/>
-      <c r="N11" s="18"/>
-      <c r="O11" s="18"/>
-      <c r="P11" s="18"/>
-      <c r="Q11" s="18"/>
-      <c r="R11" s="18"/>
-      <c r="S11" s="18"/>
-      <c r="T11" s="18"/>
-      <c r="U11" s="26" t="s">
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="L11" s="38"/>
+      <c r="M11" s="38"/>
+      <c r="N11" s="38"/>
+      <c r="O11" s="38"/>
+      <c r="P11" s="38"/>
+      <c r="Q11" s="38"/>
+      <c r="R11" s="38"/>
+      <c r="S11" s="38"/>
+      <c r="T11" s="38"/>
+      <c r="U11" s="47" t="s">
         <v>62</v>
       </c>
-      <c r="V11" s="26"/>
-      <c r="W11" s="26"/>
-      <c r="X11" s="27"/>
+      <c r="V11" s="47"/>
+      <c r="W11" s="47"/>
+      <c r="X11" s="48"/>
       <c r="Z11" s="7" t="s">
         <v>35</v>
       </c>
@@ -1469,143 +1485,143 @@
       <c r="X12" s="13"/>
     </row>
     <row r="13" spans="1:30" s="7" customFormat="1" ht="24" customHeight="1" thickBot="1">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
-      <c r="J13" s="20"/>
-      <c r="K13" s="20"/>
-      <c r="L13" s="20"/>
-      <c r="M13" s="20" t="s">
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="42"/>
+      <c r="L13" s="42"/>
+      <c r="M13" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="N13" s="20"/>
-      <c r="O13" s="20"/>
-      <c r="P13" s="20"/>
-      <c r="Q13" s="20"/>
-      <c r="R13" s="20"/>
-      <c r="S13" s="20"/>
-      <c r="T13" s="20"/>
-      <c r="U13" s="20"/>
-      <c r="V13" s="20"/>
-      <c r="W13" s="20"/>
-      <c r="X13" s="20"/>
+      <c r="N13" s="42"/>
+      <c r="O13" s="42"/>
+      <c r="P13" s="42"/>
+      <c r="Q13" s="42"/>
+      <c r="R13" s="42"/>
+      <c r="S13" s="42"/>
+      <c r="T13" s="42"/>
+      <c r="U13" s="42"/>
+      <c r="V13" s="42"/>
+      <c r="W13" s="42"/>
+      <c r="X13" s="42"/>
     </row>
     <row r="14" spans="1:30" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A14" s="28" t="s">
+      <c r="A14" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="B14" s="29"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="29"/>
-      <c r="J14" s="29"/>
-      <c r="K14" s="29"/>
-      <c r="L14" s="30"/>
-      <c r="M14" s="28" t="s">
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="18"/>
+      <c r="K14" s="18"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="N14" s="29"/>
-      <c r="O14" s="29"/>
-      <c r="P14" s="29"/>
-      <c r="Q14" s="29"/>
-      <c r="R14" s="29"/>
-      <c r="S14" s="29"/>
-      <c r="T14" s="29"/>
-      <c r="U14" s="29"/>
-      <c r="V14" s="29"/>
-      <c r="W14" s="29"/>
-      <c r="X14" s="37"/>
+      <c r="N14" s="18"/>
+      <c r="O14" s="18"/>
+      <c r="P14" s="18"/>
+      <c r="Q14" s="18"/>
+      <c r="R14" s="18"/>
+      <c r="S14" s="18"/>
+      <c r="T14" s="18"/>
+      <c r="U14" s="18"/>
+      <c r="V14" s="18"/>
+      <c r="W14" s="18"/>
+      <c r="X14" s="26"/>
     </row>
     <row r="15" spans="1:30" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A15" s="31"/>
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="32"/>
-      <c r="K15" s="32"/>
-      <c r="L15" s="33"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="32"/>
-      <c r="O15" s="32"/>
-      <c r="P15" s="32"/>
-      <c r="Q15" s="32"/>
-      <c r="R15" s="32"/>
-      <c r="S15" s="32"/>
-      <c r="T15" s="32"/>
-      <c r="U15" s="32"/>
-      <c r="V15" s="32"/>
-      <c r="W15" s="32"/>
-      <c r="X15" s="38"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="21"/>
+      <c r="O15" s="21"/>
+      <c r="P15" s="21"/>
+      <c r="Q15" s="21"/>
+      <c r="R15" s="21"/>
+      <c r="S15" s="21"/>
+      <c r="T15" s="21"/>
+      <c r="U15" s="21"/>
+      <c r="V15" s="21"/>
+      <c r="W15" s="21"/>
+      <c r="X15" s="27"/>
       <c r="AD15" s="11"/>
     </row>
     <row r="16" spans="1:30" s="7" customFormat="1" ht="24" customHeight="1">
-      <c r="A16" s="31"/>
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="32"/>
-      <c r="K16" s="32"/>
-      <c r="L16" s="33"/>
-      <c r="M16" s="31"/>
-      <c r="N16" s="32"/>
-      <c r="O16" s="32"/>
-      <c r="P16" s="32"/>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="32"/>
-      <c r="S16" s="32"/>
-      <c r="T16" s="32"/>
-      <c r="U16" s="32"/>
-      <c r="V16" s="32"/>
-      <c r="W16" s="32"/>
-      <c r="X16" s="38"/>
+      <c r="A16" s="20"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="20"/>
+      <c r="N16" s="21"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="21"/>
+      <c r="Q16" s="21"/>
+      <c r="R16" s="21"/>
+      <c r="S16" s="21"/>
+      <c r="T16" s="21"/>
+      <c r="U16" s="21"/>
+      <c r="V16" s="21"/>
+      <c r="W16" s="21"/>
+      <c r="X16" s="27"/>
     </row>
     <row r="17" spans="1:28" s="7" customFormat="1" ht="24" customHeight="1" thickBot="1">
-      <c r="A17" s="34"/>
-      <c r="B17" s="35"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="35"/>
-      <c r="J17" s="35"/>
-      <c r="K17" s="35"/>
-      <c r="L17" s="36"/>
-      <c r="M17" s="34"/>
-      <c r="N17" s="35"/>
-      <c r="O17" s="35"/>
-      <c r="P17" s="35"/>
-      <c r="Q17" s="35"/>
-      <c r="R17" s="35"/>
-      <c r="S17" s="35"/>
-      <c r="T17" s="35"/>
-      <c r="U17" s="35"/>
-      <c r="V17" s="35"/>
-      <c r="W17" s="35"/>
-      <c r="X17" s="39"/>
+      <c r="A17" s="23"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="25"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="24"/>
+      <c r="O17" s="24"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="24"/>
+      <c r="R17" s="24"/>
+      <c r="S17" s="24"/>
+      <c r="T17" s="24"/>
+      <c r="U17" s="24"/>
+      <c r="V17" s="24"/>
+      <c r="W17" s="24"/>
+      <c r="X17" s="28"/>
     </row>
     <row r="18" spans="1:28" s="7" customFormat="1" ht="24" customHeight="1">
       <c r="A18" s="10"/>
@@ -1862,7 +1878,11 @@
       <c r="W30" s="10"/>
       <c r="X30" s="10"/>
     </row>
-    <row r="31" spans="1:28" s="7" customFormat="1" ht="24" customHeight="1"/>
+    <row r="31" spans="1:28" s="7" customFormat="1" ht="24" customHeight="1">
+      <c r="Z31" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
     <row r="32" spans="1:28" s="7" customFormat="1" ht="24" customHeight="1"/>
     <row r="33" spans="1:26" s="7" customFormat="1" ht="24" customHeight="1">
       <c r="A33" s="9"/>
@@ -1979,6 +1999,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="A3:X3"/>
+    <mergeCell ref="E4:X4"/>
+    <mergeCell ref="M5:P5"/>
+    <mergeCell ref="Q5:X5"/>
+    <mergeCell ref="M6:P6"/>
+    <mergeCell ref="U11:X11"/>
+    <mergeCell ref="A13:L13"/>
+    <mergeCell ref="M13:X13"/>
+    <mergeCell ref="Q6:X6"/>
+    <mergeCell ref="M7:P7"/>
+    <mergeCell ref="Q7:X7"/>
+    <mergeCell ref="A9:X9"/>
     <mergeCell ref="F1:S2"/>
     <mergeCell ref="A1:E2"/>
     <mergeCell ref="A14:L17"/>
@@ -1995,18 +2027,6 @@
     <mergeCell ref="E10:T10"/>
     <mergeCell ref="U10:X10"/>
     <mergeCell ref="E11:T11"/>
-    <mergeCell ref="U11:X11"/>
-    <mergeCell ref="A13:L13"/>
-    <mergeCell ref="M13:X13"/>
-    <mergeCell ref="Q6:X6"/>
-    <mergeCell ref="M7:P7"/>
-    <mergeCell ref="Q7:X7"/>
-    <mergeCell ref="A9:X9"/>
-    <mergeCell ref="A3:X3"/>
-    <mergeCell ref="E4:X4"/>
-    <mergeCell ref="M5:P5"/>
-    <mergeCell ref="Q5:X5"/>
-    <mergeCell ref="M6:P6"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="1">
